--- a/file/KMP.xlsx
+++ b/file/KMP.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="7">
+  <si>
+    <t>在字符串 s 中找到 t 匹配的第一个下标</t>
+  </si>
   <si>
     <t>s</t>
   </si>
@@ -41,10 +44,10 @@
     <t>t</t>
   </si>
   <si>
-    <t>pre</t>
+    <t>suf</t>
   </si>
   <si>
-    <t>suf</t>
+    <t>pre</t>
   </si>
 </sst>
 </file>
@@ -672,13 +675,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -691,7 +703,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1222,837 +1237,1030 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="R2:AE41"/>
+  <dimension ref="R2:AE56"/>
   <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="2.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="19:31">
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+    </row>
+    <row r="3" spans="19:31">
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="19:31">
+      <c r="S4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="19:31">
-      <c r="S3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>1</v>
+      <c r="U4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="19:31">
       <c r="S5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="AA5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="19:31">
-      <c r="S6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="7" spans="19:31">
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="19:31">
       <c r="S8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="5" t="s">
-        <v>2</v>
+      <c r="U8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="19:31">
       <c r="S9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="19:31">
-      <c r="S11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE11" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="19:31">
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
     </row>
     <row r="12" spans="19:31">
       <c r="S12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="V12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X12" s="2" t="s">
+      <c r="U12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="19:31">
+      <c r="S13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="19:31">
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+    </row>
+    <row r="16" spans="19:31">
+      <c r="S16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Y12" s="3" t="s">
+      <c r="U16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="19:31">
+      <c r="S17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="19:31">
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+    </row>
+    <row r="20" spans="19:31">
+      <c r="S20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA12" s="1" t="s">
+      <c r="U20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="19:31">
+      <c r="S21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="19:31">
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+    </row>
+    <row r="24" spans="19:31">
+      <c r="S24" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="19:31">
-      <c r="S14" s="1" t="s">
+      <c r="U24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="19:31">
+      <c r="S25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="19:31">
+      <c r="S29" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+    </row>
+    <row r="30" spans="19:31">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="19:31">
+      <c r="S31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X14" s="2" t="s">
+      <c r="U31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z31" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA31" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="19:31">
+      <c r="S32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z32" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="18:27">
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="18:27">
+      <c r="R35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y35" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="18:27">
+      <c r="R36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA36" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="18:27">
+      <c r="U37" s="10"/>
+      <c r="V37" s="10">
+        <v>0</v>
+      </c>
+      <c r="W37" s="10">
+        <v>0</v>
+      </c>
+      <c r="X37" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="10">
         <v>1</v>
       </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Z37" s="6">
         <v>1</v>
       </c>
-      <c r="Z14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="1" t="s">
+      <c r="AA37" s="10"/>
+    </row>
+    <row r="38" spans="18:27">
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="10"/>
+    </row>
+    <row r="39" spans="18:27">
+      <c r="R39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U39" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X39" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y39" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA39" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="18:27">
+      <c r="R40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z40" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA40" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="18:27">
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="10"/>
+    </row>
+    <row r="42" spans="18:27">
+      <c r="U42" s="10"/>
+      <c r="V42" s="10">
+        <v>0</v>
+      </c>
+      <c r="W42" s="10">
+        <v>0</v>
+      </c>
+      <c r="X42" s="10">
         <v>1</v>
       </c>
-      <c r="AC14" s="1" t="s">
+      <c r="Y42" s="6">
         <v>1</v>
       </c>
-      <c r="AD14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="19:31">
-      <c r="S15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="18:31">
-      <c r="S17" s="1" t="s">
+      <c r="Z42" s="10"/>
+      <c r="AA42" s="10"/>
+    </row>
+    <row r="43" spans="18:27">
+      <c r="R43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z43" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="18:27">
+      <c r="R44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z44" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA44" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="18:27">
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="Z45" s="10"/>
+      <c r="AA45" s="10"/>
+    </row>
+    <row r="46" spans="18:27">
+      <c r="U46" s="9"/>
+      <c r="V46" s="9">
         <v>0</v>
       </c>
-      <c r="U17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="18:31">
-      <c r="S18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="18:31">
-      <c r="R25" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="18:31">
-      <c r="R26" s="6" t="s">
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="10"/>
+    </row>
+    <row r="47" spans="18:27">
+      <c r="R47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA26" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="18:31">
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-    </row>
-    <row r="28" spans="18:31">
-      <c r="R28" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA28" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="18:31">
-      <c r="R29" s="6" t="s">
+      <c r="U47" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V47" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="18:27">
+      <c r="R48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V48" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z48" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="18:27">
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
+      <c r="Y49" s="10"/>
+      <c r="Z49" s="10"/>
+      <c r="AA49" s="10"/>
+    </row>
+    <row r="50" spans="18:27">
+      <c r="U50" s="10"/>
+      <c r="V50" s="10">
+        <v>0</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0</v>
+      </c>
+      <c r="X50" s="10"/>
+      <c r="Y50" s="10"/>
+      <c r="Z50" s="10"/>
+      <c r="AA50" s="10"/>
+    </row>
+    <row r="51" spans="18:27">
+      <c r="R51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA29" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="18:31">
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
-    </row>
-    <row r="31" spans="18:31">
-      <c r="R31" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="U31" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="18:31">
-      <c r="R32" s="6" t="s">
+      <c r="U51" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W51" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X51" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z51" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA51" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="18:27">
+      <c r="R52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V52" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z52" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="18:27">
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+    </row>
+    <row r="54" spans="18:27">
+      <c r="U54" s="10"/>
+      <c r="V54" s="6">
+        <v>0</v>
+      </c>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10"/>
+      <c r="AA54" s="10"/>
+    </row>
+    <row r="55" spans="18:27">
+      <c r="R55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X32" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA32" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="18:31">
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
-      <c r="AA33" s="7"/>
-    </row>
-    <row r="34" spans="18:31">
-      <c r="R34" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V34" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W34" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA34" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE34" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="18:31">
-      <c r="R35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W35" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA35" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="18:31">
-      <c r="U36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
-    </row>
-    <row r="37" spans="18:31">
-      <c r="R37" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="U37" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V37" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W37" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE37" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="18:31">
-      <c r="R38" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V38" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W38" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA38" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="18:31">
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="7"/>
-    </row>
-    <row r="40" spans="18:31">
-      <c r="S40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA40" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE40" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="18:31">
-      <c r="S41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="X41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA41" s="7" t="s">
-        <v>1</v>
+      <c r="U55" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V55" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="W55" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X55" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z55" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA55" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="18:27">
+      <c r="R56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U56" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V56" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="W56" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X56" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z56" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA56" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R34:S34"/>
+  <mergeCells count="14">
+    <mergeCell ref="S2:AE2"/>
+    <mergeCell ref="S29:AE29"/>
     <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/file/KMP.xlsx
+++ b/file/KMP.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="8">
   <si>
     <t>在字符串 s 中找到 t 匹配的第一个下标</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>t</t>
+  </si>
+  <si>
+    <t>如何预处理 t 中子串最长公共前后缀</t>
   </si>
   <si>
     <t>suf</t>
@@ -675,7 +678,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -703,14 +706,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1237,1030 +1234,1513 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="R2:AE56"/>
+  <dimension ref="F2:AR57"/>
   <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="2.625" style="1" customWidth="1"/>
+    <col min="1" max="16377" width="2.625" style="1" customWidth="1"/>
+    <col min="16378" max="16384" width="2.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="19:31">
-      <c r="S2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-    </row>
-    <row r="3" spans="19:31">
-      <c r="U3" s="3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="1">
+    <row r="2" spans="7:19">
+      <c r="G2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+    </row>
+    <row r="3" spans="7:19">
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="19:31">
+    <row r="4" spans="7:19">
+      <c r="G4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="S4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="7:19">
+      <c r="G5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="7:19">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" spans="7:19">
+      <c r="G8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="19:31">
-      <c r="S5" s="1" t="s">
+      <c r="I8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="7:19">
+      <c r="G9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="19:31">
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-    </row>
-    <row r="8" spans="19:31">
-      <c r="S8" s="1" t="s">
+      <c r="I9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="7:19">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="12" spans="7:19">
+      <c r="G12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="19:31">
-      <c r="S9" s="1" t="s">
+      <c r="I12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="7:19">
+      <c r="G13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="19:31">
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-    </row>
-    <row r="12" spans="19:31">
-      <c r="S12" s="1" t="s">
+      <c r="I13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="7:19">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="16" spans="7:19">
+      <c r="G16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U12" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y12" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="19:31">
-      <c r="S13" s="1" t="s">
+      <c r="I16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="6:44">
+      <c r="G17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="19:31">
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-    </row>
-    <row r="16" spans="19:31">
-      <c r="S16" s="1" t="s">
+      <c r="I17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="6:44">
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="20" spans="6:44">
+      <c r="G20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U16" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="19:31">
-      <c r="S17" s="1" t="s">
+      <c r="I20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="6:44">
+      <c r="G21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="19:31">
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-    </row>
-    <row r="20" spans="19:31">
-      <c r="S20" s="1" t="s">
+      <c r="I21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="6:44">
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="24" spans="6:44">
+      <c r="G24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y20" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE20" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="19:31">
-      <c r="S21" s="1" t="s">
+      <c r="I24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="6:44">
+      <c r="G25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y21" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z21" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="19:31">
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-    </row>
-    <row r="24" spans="19:31">
-      <c r="S24" s="1" t="s">
+      <c r="I25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="6:44">
+      <c r="G29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+    </row>
+    <row r="30" spans="6:44">
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="6:44">
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6">
         <v>1</v>
       </c>
-      <c r="U24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="19:31">
-      <c r="S25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z25" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA25" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="19:31">
-      <c r="S29" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="2"/>
-      <c r="AE29" s="2"/>
-    </row>
-    <row r="30" spans="19:31">
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="1">
+      <c r="AI31" s="9"/>
+      <c r="AJ31" s="9"/>
+      <c r="AL31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="4"/>
+      <c r="AR31" s="4"/>
+    </row>
+    <row r="32" spans="6:44">
+      <c r="F32" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="I32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI32" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ32" s="9"/>
+      <c r="AL32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR32" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="6:44">
+      <c r="F33" s="9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="19:31">
-      <c r="S31" s="1" t="s">
+      <c r="G33" s="9"/>
+      <c r="I33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ33" s="9"/>
+      <c r="AL33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR33" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="6:44">
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="6:44">
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2</v>
+      </c>
+      <c r="N35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="9"/>
+      <c r="AJ35" s="9"/>
+      <c r="AL35" s="4"/>
+      <c r="AM35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="4"/>
+      <c r="AP35" s="4"/>
+      <c r="AQ35" s="4"/>
+      <c r="AR35" s="4"/>
+    </row>
+    <row r="36" spans="6:44">
+      <c r="F36" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="9"/>
+      <c r="I36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI36" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ36" s="9"/>
+      <c r="AL36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN36" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP36" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR36" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="6:44">
+      <c r="F37" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="9"/>
+      <c r="I37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI37" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ37" s="9"/>
+      <c r="AL37" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP37" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR37" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="6:44">
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="I38" s="4"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="6:44">
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>0</v>
+      </c>
+      <c r="M39" s="6">
         <v>1</v>
       </c>
-      <c r="U31" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V31" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W31" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X31" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y31" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z31" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA31" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="19:31">
-      <c r="S32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y32" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z32" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="18:27">
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="18:27">
-      <c r="R35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z35" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="18:27">
-      <c r="R36" s="1" t="s">
+      <c r="O39" s="4"/>
+      <c r="AI39" s="9"/>
+      <c r="AJ39" s="9"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="4"/>
+    </row>
+    <row r="40" spans="6:44">
+      <c r="F40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="U36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z36" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA36" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="18:27">
-      <c r="U37" s="10"/>
-      <c r="V37" s="10">
-        <v>0</v>
-      </c>
-      <c r="W37" s="10">
-        <v>0</v>
-      </c>
-      <c r="X37" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="10">
+      <c r="G40" s="9"/>
+      <c r="I40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI40" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ40" s="9"/>
+      <c r="AL40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP40" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR40" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="6:44">
+      <c r="F41" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="9"/>
+      <c r="I41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI41" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ41" s="9"/>
+      <c r="AL41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR41" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="6:44">
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="6:44">
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="6">
         <v>1</v>
       </c>
-      <c r="Z37" s="6">
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="AI43" s="9"/>
+      <c r="AJ43" s="9"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
         <v>1</v>
       </c>
-      <c r="AA37" s="10"/>
-    </row>
-    <row r="38" spans="18:27">
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="11"/>
-      <c r="Z38" s="11"/>
-      <c r="AA38" s="10"/>
-    </row>
-    <row r="39" spans="18:27">
-      <c r="R39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U39" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V39" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X39" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z39" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA39" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="18:27">
-      <c r="R40" s="1" t="s">
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+    </row>
+    <row r="44" spans="6:44">
+      <c r="F44" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="U40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y40" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z40" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA40" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="18:27">
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="11"/>
-      <c r="Z41" s="11"/>
-      <c r="AA41" s="10"/>
-    </row>
-    <row r="42" spans="18:27">
-      <c r="U42" s="10"/>
-      <c r="V42" s="10">
-        <v>0</v>
-      </c>
-      <c r="W42" s="10">
-        <v>0</v>
-      </c>
-      <c r="X42" s="10">
+      <c r="G44" s="9"/>
+      <c r="I44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI44" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ44" s="9"/>
+      <c r="AL44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO44" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP44" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR44" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="6:44">
+      <c r="F45" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="9"/>
+      <c r="I45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI45" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ45" s="9"/>
+      <c r="AL45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR45" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="6:44">
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="6:44">
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="AI47" s="9"/>
+      <c r="AJ47" s="9"/>
+      <c r="AL47" s="3"/>
+      <c r="AM47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="6">
         <v>1</v>
       </c>
-      <c r="Y42" s="6">
+      <c r="AR47" s="4"/>
+    </row>
+    <row r="48" spans="6:44">
+      <c r="F48" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="9"/>
+      <c r="I48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI48" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ48" s="9"/>
+      <c r="AL48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP48" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR48" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="6:44">
+      <c r="F49" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="9"/>
+      <c r="I49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI49" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ49" s="9"/>
+      <c r="AL49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP49" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR49" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="6:44">
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="6:44">
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="AI51" s="9"/>
+      <c r="AJ51" s="9"/>
+      <c r="AM51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ51" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="6:44">
+      <c r="F52" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="9"/>
+      <c r="I52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI52" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ52" s="9"/>
+      <c r="AL52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO52" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP52" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR52" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="6:44">
+      <c r="F53" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="9"/>
+      <c r="I53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI53" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ53" s="9"/>
+      <c r="AL53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR53" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="6:44">
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" spans="6:44">
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="I55" s="6">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="AM55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR55" s="6">
         <v>1</v>
       </c>
-      <c r="Z42" s="10"/>
-      <c r="AA42" s="10"/>
-    </row>
-    <row r="43" spans="18:27">
-      <c r="R43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U43" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V43" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W43" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y43" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z43" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA43" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="18:27">
-      <c r="R44" s="1" t="s">
+    </row>
+    <row r="56" spans="6:44">
+      <c r="F56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="U44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="X44" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y44" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z44" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA44" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="18:27">
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="10"/>
-      <c r="AA45" s="10"/>
-    </row>
-    <row r="46" spans="18:27">
-      <c r="U46" s="9"/>
-      <c r="V46" s="9">
-        <v>0</v>
-      </c>
-      <c r="W46" s="9">
-        <v>0</v>
-      </c>
-      <c r="X46" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11"/>
-      <c r="AA46" s="10"/>
-    </row>
-    <row r="47" spans="18:27">
-      <c r="R47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V47" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y47" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z47" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA47" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="18:27">
-      <c r="R48" s="1" t="s">
+      <c r="G56" s="9"/>
+      <c r="I56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="U48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V48" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y48" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z48" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA48" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="18:27">
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="X49" s="10"/>
-      <c r="Y49" s="10"/>
-      <c r="Z49" s="10"/>
-      <c r="AA49" s="10"/>
-    </row>
-    <row r="50" spans="18:27">
-      <c r="U50" s="10"/>
-      <c r="V50" s="10">
-        <v>0</v>
-      </c>
-      <c r="W50" s="6">
-        <v>0</v>
-      </c>
-      <c r="X50" s="10"/>
-      <c r="Y50" s="10"/>
-      <c r="Z50" s="10"/>
-      <c r="AA50" s="10"/>
-    </row>
-    <row r="51" spans="18:27">
-      <c r="R51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U51" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V51" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="W51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X51" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y51" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA51" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="18:27">
-      <c r="R52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U52" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y52" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z52" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA52" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="18:27">
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-    </row>
-    <row r="54" spans="18:27">
-      <c r="U54" s="10"/>
-      <c r="V54" s="6">
-        <v>0</v>
-      </c>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10"/>
-      <c r="AA54" s="10"/>
-    </row>
-    <row r="55" spans="18:27">
-      <c r="R55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U55" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V55" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="W55" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X55" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y55" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z55" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="18:27">
-      <c r="R56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U56" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V56" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="W56" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X56" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y56" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z56" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA56" s="10" t="s">
+      <c r="AJ56" s="9"/>
+      <c r="AL56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM56" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN56" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP56" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ56" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR56" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="6:44">
+      <c r="F57" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="9"/>
+      <c r="I57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI57" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ57" s="9"/>
+      <c r="AL57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM57" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN57" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ57" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR57" s="4" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="S2:AE2"/>
-    <mergeCell ref="S29:AE29"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
+  <mergeCells count="30">
+    <mergeCell ref="G2:S2"/>
+    <mergeCell ref="G29:S29"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="AI32:AJ32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="AI33:AJ33"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="AI37:AJ37"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="AI40:AJ40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="AI41:AJ41"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="AI44:AJ44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="AI45:AJ45"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="AI48:AJ48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="AI49:AJ49"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="AI52:AJ52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="AI53:AJ53"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="AI56:AJ56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="AI57:AJ57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
